--- a/2° semestre/Banco de Dados/18-09/dicionario_aluno.xlsx
+++ b/2° semestre/Banco de Dados/18-09/dicionario_aluno.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Aluno\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21FADB94-F4AA-44BE-B60B-6323DC499020}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4A4C205-007E-4BC4-A695-8C0C2C78CEC5}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="6930" xr2:uid="{37811BB3-0479-4227-A9B2-56A25E6E88FC}"/>
   </bookViews>
@@ -27,9 +27,6 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="39">
   <si>
-    <t>Armazena as informações dos empréstimos</t>
-  </si>
-  <si>
     <t>Nome</t>
   </si>
   <si>
@@ -142,6 +139,9 @@
   </si>
   <si>
     <t>Carga horária do curso em minutos</t>
+  </si>
+  <si>
+    <t>Armazena as informações das matrículas</t>
   </si>
 </sst>
 </file>
@@ -239,9 +239,6 @@
   </cellStyleXfs>
   <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -252,17 +249,20 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -587,13 +587,13 @@
     <col min="4" max="4" width="12.08984375" customWidth="1"/>
     <col min="5" max="5" width="22.81640625" customWidth="1"/>
     <col min="6" max="6" width="22.6328125" customWidth="1"/>
-    <col min="8" max="8" width="12.6328125" style="2" customWidth="1"/>
-    <col min="9" max="9" width="22.36328125" style="2" customWidth="1"/>
-    <col min="10" max="10" width="14.08984375" style="2" customWidth="1"/>
-    <col min="11" max="11" width="12.08984375" style="2" customWidth="1"/>
-    <col min="12" max="12" width="22.81640625" style="2" customWidth="1"/>
-    <col min="13" max="13" width="22.6328125" style="2" customWidth="1"/>
-    <col min="15" max="15" width="13" style="2" customWidth="1"/>
+    <col min="8" max="8" width="12.6328125" style="1" customWidth="1"/>
+    <col min="9" max="9" width="22.36328125" style="1" customWidth="1"/>
+    <col min="10" max="10" width="14.08984375" style="1" customWidth="1"/>
+    <col min="11" max="11" width="12.08984375" style="1" customWidth="1"/>
+    <col min="12" max="12" width="22.81640625" style="1" customWidth="1"/>
+    <col min="13" max="13" width="22.6328125" style="1" customWidth="1"/>
+    <col min="15" max="15" width="13" style="1" customWidth="1"/>
     <col min="16" max="16" width="21.90625" customWidth="1"/>
     <col min="17" max="17" width="13.36328125" customWidth="1"/>
     <col min="18" max="18" width="12" customWidth="1"/>
@@ -602,352 +602,352 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:20" x14ac:dyDescent="0.35">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B1" s="4"/>
+      <c r="C1" s="4"/>
+      <c r="D1" s="4"/>
+      <c r="E1" s="4"/>
+      <c r="F1" s="4"/>
+      <c r="H1" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="I1" s="4"/>
+      <c r="J1" s="4"/>
+      <c r="K1" s="4"/>
+      <c r="L1" s="4"/>
+      <c r="M1" s="4"/>
+      <c r="O1" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="P1" s="4"/>
+      <c r="Q1" s="4"/>
+      <c r="R1" s="4"/>
+      <c r="S1" s="4"/>
+      <c r="T1" s="4"/>
+    </row>
+    <row r="2" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="A2" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="B1" s="5"/>
-      <c r="C1" s="5"/>
-      <c r="D1" s="5"/>
-      <c r="E1" s="5"/>
-      <c r="F1" s="5"/>
-      <c r="H1" s="5" t="s">
+      <c r="B2" s="4"/>
+      <c r="C2" s="4"/>
+      <c r="D2" s="4"/>
+      <c r="E2" s="4"/>
+      <c r="F2" s="4"/>
+      <c r="H2" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="I1" s="5"/>
-      <c r="J1" s="5"/>
-      <c r="K1" s="5"/>
-      <c r="L1" s="5"/>
-      <c r="M1" s="5"/>
-      <c r="O1" s="5" t="s">
+      <c r="I2" s="4"/>
+      <c r="J2" s="4"/>
+      <c r="K2" s="4"/>
+      <c r="L2" s="4"/>
+      <c r="M2" s="4"/>
+      <c r="O2" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="P2" s="4"/>
+      <c r="Q2" s="4"/>
+      <c r="R2" s="4"/>
+      <c r="S2" s="4"/>
+      <c r="T2" s="4"/>
+    </row>
+    <row r="3" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="A3" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="J3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="K3" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="L3" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="M3" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="O3" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="P3" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="R3" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="S3" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="T3" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="A4" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4" s="3"/>
+      <c r="C4" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D4" s="3"/>
+      <c r="E4" s="3"/>
+      <c r="F4" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="I4" s="3"/>
+      <c r="J4" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="K4" s="3"/>
+      <c r="L4" s="3"/>
+      <c r="M4" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O4" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="P4" s="3"/>
+      <c r="Q4" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="R4" s="3"/>
+      <c r="S4" s="3"/>
+      <c r="T4" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5" spans="1:20" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="C5" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="D5" s="9">
+        <v>80</v>
+      </c>
+      <c r="E5" s="8"/>
+      <c r="F5" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="H5" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="I5" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="J5" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="K5" s="9">
+        <v>80</v>
+      </c>
+      <c r="L5" s="8"/>
+      <c r="M5" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="O5" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="P5" s="3"/>
+      <c r="Q5" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="R5" s="3"/>
+      <c r="S5" s="3"/>
+      <c r="T5" s="3" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="6" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="A6" s="8"/>
+      <c r="B6" s="7"/>
+      <c r="C6" s="8"/>
+      <c r="D6" s="9"/>
+      <c r="E6" s="8"/>
+      <c r="F6" s="8"/>
+      <c r="H6" s="8"/>
+      <c r="I6" s="7"/>
+      <c r="J6" s="8"/>
+      <c r="K6" s="9"/>
+      <c r="L6" s="8"/>
+      <c r="M6" s="8"/>
+      <c r="O6" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="P6" s="3"/>
+      <c r="Q6" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="R6" s="3"/>
+      <c r="S6" s="3"/>
+      <c r="T6" s="3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="7" spans="1:20" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C7" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="D7" s="9">
+        <v>11</v>
+      </c>
+      <c r="E7" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="F7" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="H7" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="I7" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="J7" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="K7" s="9"/>
+      <c r="L7" s="8"/>
+      <c r="M7" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="O7" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="P7" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="P1" s="5"/>
-      <c r="Q1" s="5"/>
-      <c r="R1" s="5"/>
-      <c r="S1" s="5"/>
-      <c r="T1" s="5"/>
-    </row>
-    <row r="2" spans="1:20" x14ac:dyDescent="0.35">
-      <c r="A2" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="B2" s="5"/>
-      <c r="C2" s="5"/>
-      <c r="D2" s="5"/>
-      <c r="E2" s="5"/>
-      <c r="F2" s="5"/>
-      <c r="H2" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="I2" s="5"/>
-      <c r="J2" s="5"/>
-      <c r="K2" s="5"/>
-      <c r="L2" s="5"/>
-      <c r="M2" s="5"/>
-      <c r="O2" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="P2" s="5"/>
-      <c r="Q2" s="5"/>
-      <c r="R2" s="5"/>
-      <c r="S2" s="5"/>
-      <c r="T2" s="5"/>
-    </row>
-    <row r="3" spans="1:20" x14ac:dyDescent="0.35">
-      <c r="A3" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="H3" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="I3" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="J3" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K3" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="L3" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M3" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="O3" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="P3" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="Q3" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R3" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="S3" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T3" s="3" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="4" spans="1:20" x14ac:dyDescent="0.35">
-      <c r="A4" s="4" t="s">
+      <c r="Q7" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="R7" s="9"/>
+      <c r="S7" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="T7" s="8" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="8" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="A8" s="8"/>
+      <c r="B8" s="7"/>
+      <c r="C8" s="8"/>
+      <c r="D8" s="9"/>
+      <c r="E8" s="8"/>
+      <c r="F8" s="8"/>
+      <c r="H8" s="8"/>
+      <c r="I8" s="7"/>
+      <c r="J8" s="8"/>
+      <c r="K8" s="9"/>
+      <c r="L8" s="8"/>
+      <c r="M8" s="8"/>
+      <c r="O8" s="6"/>
+      <c r="P8" s="7"/>
+      <c r="Q8" s="8"/>
+      <c r="R8" s="9"/>
+      <c r="S8" s="8"/>
+      <c r="T8" s="8"/>
+    </row>
+    <row r="9" spans="1:20" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="B9" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C9" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="D9" s="9">
+        <v>50</v>
+      </c>
+      <c r="E9" s="8"/>
+      <c r="F9" s="8"/>
+      <c r="H9" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="I9" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="J9" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="B4" s="4"/>
-      <c r="C4" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D4" s="4"/>
-      <c r="E4" s="4"/>
-      <c r="F4" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="H4" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="I4" s="4"/>
-      <c r="J4" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="K4" s="4"/>
-      <c r="L4" s="4"/>
-      <c r="M4" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="O4" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="P4" s="4"/>
-      <c r="Q4" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="R4" s="4"/>
-      <c r="S4" s="4"/>
-      <c r="T4" s="4" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="5" spans="1:20" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="B5" s="6" t="s">
+      <c r="K9" s="9"/>
+      <c r="L9" s="8"/>
+      <c r="M9" s="8" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="10" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="A10" s="8"/>
+      <c r="B10" s="7"/>
+      <c r="C10" s="8"/>
+      <c r="D10" s="9"/>
+      <c r="E10" s="8"/>
+      <c r="F10" s="8"/>
+      <c r="H10" s="8"/>
+      <c r="I10" s="7"/>
+      <c r="J10" s="8"/>
+      <c r="K10" s="9"/>
+      <c r="L10" s="8"/>
+      <c r="M10" s="8"/>
+    </row>
+    <row r="11" spans="1:20" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="B11" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="C11" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="C5" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="D5" s="7">
-        <v>80</v>
-      </c>
-      <c r="E5" s="1"/>
-      <c r="F5" s="1" t="s">
+      <c r="D11" s="9">
         <v>11</v>
       </c>
-      <c r="H5" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="I5" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="J5" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="K5" s="7">
-        <v>80</v>
-      </c>
-      <c r="L5" s="1"/>
-      <c r="M5" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="O5" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="P5" s="4"/>
-      <c r="Q5" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="R5" s="4"/>
-      <c r="S5" s="4"/>
-      <c r="T5" s="4" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.35">
-      <c r="A6" s="1"/>
-      <c r="B6" s="6"/>
-      <c r="C6" s="1"/>
-      <c r="D6" s="7"/>
-      <c r="E6" s="1"/>
-      <c r="F6" s="1"/>
-      <c r="H6" s="1"/>
-      <c r="I6" s="6"/>
-      <c r="J6" s="1"/>
-      <c r="K6" s="7"/>
-      <c r="L6" s="1"/>
-      <c r="M6" s="1"/>
-      <c r="O6" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="P6" s="4"/>
-      <c r="Q6" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="R6" s="4"/>
-      <c r="S6" s="4"/>
-      <c r="T6" s="4" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="7" spans="1:20" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B7" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="D7" s="7">
-        <v>11</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="F7" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="H7" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="I7" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="J7" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="K7" s="7"/>
-      <c r="L7" s="1"/>
-      <c r="M7" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="O7" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="P7" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="Q7" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="R7" s="7"/>
-      <c r="S7" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="T7" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.35">
-      <c r="A8" s="1"/>
-      <c r="B8" s="6"/>
-      <c r="C8" s="1"/>
-      <c r="D8" s="7"/>
-      <c r="E8" s="1"/>
-      <c r="F8" s="1"/>
-      <c r="H8" s="1"/>
-      <c r="I8" s="6"/>
-      <c r="J8" s="1"/>
-      <c r="K8" s="7"/>
-      <c r="L8" s="1"/>
-      <c r="M8" s="1"/>
-      <c r="O8" s="9"/>
-      <c r="P8" s="6"/>
-      <c r="Q8" s="1"/>
-      <c r="R8" s="7"/>
-      <c r="S8" s="1"/>
-      <c r="T8" s="1"/>
-    </row>
-    <row r="9" spans="1:20" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="B9" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="D9" s="7">
-        <v>50</v>
-      </c>
-      <c r="E9" s="1"/>
-      <c r="F9" s="1"/>
-      <c r="H9" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="I9" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="J9" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="K9" s="7"/>
-      <c r="L9" s="1"/>
-      <c r="M9" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="10" spans="1:20" x14ac:dyDescent="0.35">
-      <c r="A10" s="1"/>
-      <c r="B10" s="6"/>
-      <c r="C10" s="1"/>
-      <c r="D10" s="7"/>
-      <c r="E10" s="1"/>
-      <c r="F10" s="1"/>
-      <c r="H10" s="1"/>
-      <c r="I10" s="6"/>
-      <c r="J10" s="1"/>
-      <c r="K10" s="7"/>
-      <c r="L10" s="1"/>
-      <c r="M10" s="1"/>
-    </row>
-    <row r="11" spans="1:20" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="B11" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="D11" s="7">
-        <v>11</v>
-      </c>
-      <c r="E11" s="1"/>
-      <c r="F11" s="1"/>
+      <c r="E11" s="8"/>
+      <c r="F11" s="8"/>
       <c r="H11"/>
       <c r="I11"/>
       <c r="J11"/>
@@ -956,12 +956,12 @@
       <c r="M11"/>
     </row>
     <row r="12" spans="1:20" x14ac:dyDescent="0.35">
-      <c r="A12" s="1"/>
-      <c r="B12" s="6"/>
-      <c r="C12" s="1"/>
-      <c r="D12" s="7"/>
-      <c r="E12" s="1"/>
-      <c r="F12" s="1"/>
+      <c r="A12" s="8"/>
+      <c r="B12" s="7"/>
+      <c r="C12" s="8"/>
+      <c r="D12" s="9"/>
+      <c r="E12" s="8"/>
+      <c r="F12" s="8"/>
       <c r="H12"/>
       <c r="I12"/>
       <c r="J12"/>
@@ -971,19 +971,31 @@
     </row>
   </sheetData>
   <mergeCells count="54">
-    <mergeCell ref="O1:T1"/>
-    <mergeCell ref="O2:T2"/>
-    <mergeCell ref="O7:O8"/>
-    <mergeCell ref="P7:P8"/>
-    <mergeCell ref="Q7:Q8"/>
-    <mergeCell ref="R7:R8"/>
-    <mergeCell ref="S7:S8"/>
-    <mergeCell ref="T7:T8"/>
-    <mergeCell ref="I9:I10"/>
-    <mergeCell ref="J9:J10"/>
-    <mergeCell ref="K9:K10"/>
-    <mergeCell ref="L9:L10"/>
-    <mergeCell ref="M9:M10"/>
+    <mergeCell ref="F5:F6"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A5:A6"/>
+    <mergeCell ref="B5:B6"/>
+    <mergeCell ref="C5:C6"/>
+    <mergeCell ref="D5:D6"/>
+    <mergeCell ref="E5:E6"/>
+    <mergeCell ref="F7:F8"/>
+    <mergeCell ref="A9:A10"/>
+    <mergeCell ref="B9:B10"/>
+    <mergeCell ref="C9:C10"/>
+    <mergeCell ref="D9:D10"/>
+    <mergeCell ref="E9:E10"/>
+    <mergeCell ref="F9:F10"/>
+    <mergeCell ref="A7:A8"/>
+    <mergeCell ref="B7:B8"/>
+    <mergeCell ref="C7:C8"/>
+    <mergeCell ref="D7:D8"/>
+    <mergeCell ref="E7:E8"/>
+    <mergeCell ref="A11:A12"/>
+    <mergeCell ref="B11:B12"/>
+    <mergeCell ref="C11:C12"/>
+    <mergeCell ref="D11:D12"/>
+    <mergeCell ref="E11:E12"/>
     <mergeCell ref="F11:F12"/>
     <mergeCell ref="H1:M1"/>
     <mergeCell ref="H2:M2"/>
@@ -1000,31 +1012,19 @@
     <mergeCell ref="L7:L8"/>
     <mergeCell ref="M7:M8"/>
     <mergeCell ref="H9:H10"/>
-    <mergeCell ref="A11:A12"/>
-    <mergeCell ref="B11:B12"/>
-    <mergeCell ref="C11:C12"/>
-    <mergeCell ref="D11:D12"/>
-    <mergeCell ref="E11:E12"/>
-    <mergeCell ref="F7:F8"/>
-    <mergeCell ref="A9:A10"/>
-    <mergeCell ref="B9:B10"/>
-    <mergeCell ref="C9:C10"/>
-    <mergeCell ref="D9:D10"/>
-    <mergeCell ref="E9:E10"/>
-    <mergeCell ref="F9:F10"/>
-    <mergeCell ref="A7:A8"/>
-    <mergeCell ref="B7:B8"/>
-    <mergeCell ref="C7:C8"/>
-    <mergeCell ref="D7:D8"/>
-    <mergeCell ref="E7:E8"/>
-    <mergeCell ref="F5:F6"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A5:A6"/>
-    <mergeCell ref="B5:B6"/>
-    <mergeCell ref="C5:C6"/>
-    <mergeCell ref="D5:D6"/>
-    <mergeCell ref="E5:E6"/>
+    <mergeCell ref="I9:I10"/>
+    <mergeCell ref="J9:J10"/>
+    <mergeCell ref="K9:K10"/>
+    <mergeCell ref="L9:L10"/>
+    <mergeCell ref="M9:M10"/>
+    <mergeCell ref="O1:T1"/>
+    <mergeCell ref="O2:T2"/>
+    <mergeCell ref="O7:O8"/>
+    <mergeCell ref="P7:P8"/>
+    <mergeCell ref="Q7:Q8"/>
+    <mergeCell ref="R7:R8"/>
+    <mergeCell ref="S7:S8"/>
+    <mergeCell ref="T7:T8"/>
   </mergeCells>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
